--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486415_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486415_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. NGOM</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3227</v>
+        <v>4.1547</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0876</v>
+        <v>2.7307</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2351</v>
+        <v>1.424</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9621</v>
+        <v>2.0896</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3263</v>
+        <v>-0.3743</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3642</v>
+        <v>2.4639</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6865</v>
+        <v>2.8268</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6482</v>
+        <v>0.1095</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0382</v>
+        <v>2.7173</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2757</v>
+        <v>-0.7372</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6781</v>
+        <v>-0.4838</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4024</v>
+        <v>-0.2534</v>
       </c>
       <c r="P2" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R2" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7863</v>
+        <v>0.5426</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0106</v>
+        <v>0.1214</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.4212</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2692</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>A. NGOM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1466</v>
+        <v>3.5665</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6802</v>
+        <v>1.4855</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5336</v>
+        <v>2.081</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7518</v>
+        <v>0.9621</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.3263</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0239</v>
+        <v>-0.3642</v>
       </c>
       <c r="J3" t="n">
-        <v>2.517</v>
+        <v>0.6865</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2875</v>
+        <v>0.6482</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2295</v>
+        <v>0.0382</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7652</v>
+        <v>0.2757</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5118</v>
+        <v>0.6781</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2534</v>
+        <v>-0.4024</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5895</v>
+        <v>1.0302</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6427</v>
+        <v>0.4086</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0532</v>
+        <v>0.6216</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3698</v>
+        <v>0.2692</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5204</v>
+        <v>0.3904</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.8902</v>
+        <v>-0.1213</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6345</v>
+        <v>3.2285</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3954</v>
+        <v>4.8546</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2391</v>
+        <v>-1.6261</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0896</v>
+        <v>0.7518</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3743</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4639</v>
+        <v>-0.0239</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8268</v>
+        <v>2.517</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1095</v>
+        <v>2.2875</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7173</v>
+        <v>0.2295</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7372</v>
+        <v>-1.7652</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4838</v>
+        <v>-1.5118</v>
       </c>
       <c r="O4" t="n">
         <v>-0.2534</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0224</v>
+        <v>0.6715</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2139</v>
+        <v>0.8172</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2362</v>
+        <v>-0.1457</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.51</v>
+        <v>2.1976</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4344</v>
+        <v>-1.1161</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0756</v>
+        <v>3.3138</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8808</v>
+        <v>1.0599</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4417</v>
+        <v>0.5443</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4391</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5406</v>
+        <v>0.8871</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3166</v>
+        <v>0.3317</v>
       </c>
       <c r="L5" t="n">
-        <v>1.224</v>
+        <v>0.5554</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3402</v>
+        <v>0.1728</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1251</v>
+        <v>0.2127</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7849</v>
+        <v>-0.0399</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3926</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3378</v>
+        <v>0.6717</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0911</v>
+        <v>0.1719</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2466</v>
+        <v>0.4999</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.056</v>
+        <v>0.2485</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2512</v>
+        <v>0.2485</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7248</v>
+        <v>1.9465</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1505</v>
+        <v>0.0558</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5742</v>
+        <v>1.8907</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0726</v>
+        <v>1.8808</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.028</v>
+        <v>1.4417</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0446</v>
+        <v>0.4391</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9771</v>
+        <v>1.5406</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1523</v>
+        <v>0.3166</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8248</v>
+        <v>1.224</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0497</v>
+        <v>0.3402</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1803</v>
+        <v>1.1251</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8694</v>
+        <v>-0.7849</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5225</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6101</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5706</v>
+        <v>1.7743</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6307</v>
+        <v>0.7126</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0601</v>
+        <v>1.0617</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2958</v>
+        <v>-1.056</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3698</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>0.074</v>
+        <v>-1.2512</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5018</v>
+        <v>0.8307</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8119</v>
+        <v>0.2565</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3138</v>
+        <v>0.5742</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0599</v>
+        <v>-1.0726</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5443</v>
+        <v>-1.028</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5155999999999999</v>
+        <v>-0.0446</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8871</v>
+        <v>0.9771</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3317</v>
+        <v>0.1523</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5554</v>
+        <v>0.8248</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1728</v>
+        <v>-2.0497</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2127</v>
+        <v>-1.1803</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0399</v>
+        <v>-0.8694</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3926</v>
+        <v>2.6101</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.024</v>
+        <v>0.6766</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5239</v>
+        <v>0.7367</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4999</v>
+        <v>-0.0601</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2485</v>
+        <v>-0.2958</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2485</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.725</v>
+        <v>0.3792</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4081</v>
+        <v>-0.4888</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.868</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3759</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2192</v>
+        <v>0.8851</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.536</v>
+        <v>0.3833</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3168</v>
+        <v>0.5017</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.3986</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1927</v>
+        <v>-1.6772</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4019</v>
+        <v>1.2786</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5095</v>
@@ -1156,13 +1156,13 @@
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3288</v>
+        <v>0.721</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3425</v>
+        <v>0.173</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6713</v>
+        <v>0.548</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6563</v>
+        <v>-1.029</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8655</v>
+        <v>-1.2382</v>
       </c>
       <c r="F10" t="n">
         <v>0.2092</v>
@@ -1234,10 +1234,10 @@
         <v>2.8276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6645</v>
+        <v>-0.0373</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4554</v>
+        <v>0.1719</v>
       </c>
       <c r="U10" t="n">
         <v>-0.2091</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9204</v>
+        <v>-1.4435</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.768</v>
+        <v>-1.476</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1524</v>
+        <v>0.0325</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8883</v>
@@ -1312,13 +1312,13 @@
         <v>2.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4247</v>
+        <v>0.0523</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0649</v>
+        <v>0.2271</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3598</v>
+        <v>-0.1749</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5649999999999999</v>
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.7479</v>
+        <v>13.4326</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7019</v>
+        <v>3.3868</v>
       </c>
       <c r="F12" t="n">
         <v>10.0459</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0922</v>
+        <v>1.092200000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6696999999999993</v>
+        <v>0.6696999999999997</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4224999999999998</v>
+        <v>0.4225000000000002</v>
       </c>
       <c r="J12" t="n">
         <v>7.472200000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3482</v>
+        <v>3.348199999999999</v>
       </c>
       <c r="L12" t="n">
         <v>4.1239</v>
@@ -1390,13 +1390,13 @@
         <v>18.4882</v>
       </c>
       <c r="S12" t="n">
-        <v>6.303000000000001</v>
+        <v>6.988</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2385</v>
+        <v>3.9237</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0643</v>
+        <v>3.064300000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2599</v>
@@ -1405,7 +1405,7 @@
         <v>2.8662</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.126200000000001</v>
+        <v>-5.126199999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7608</v>
+        <v>0.9034</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1064</v>
+        <v>0.0054</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8672</v>
+        <v>0.898</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7302</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5515</v>
+        <v>-0.4089</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5732</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1335</v>
+        <v>0.1643</v>
       </c>
       <c r="V13" t="n">
         <v>2.2599</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1602</v>
+        <v>-0.2809</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2954</v>
+        <v>-0.0959</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4557</v>
+        <v>-0.185</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5628</v>
+        <v>-0.9226</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0213</v>
+        <v>-1.3473</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5841</v>
+        <v>0.4247</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2235</v>
+        <v>0.8961</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.465</v>
+        <v>-0.1</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6885</v>
+        <v>0.9961</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3393</v>
+        <v>-1.8187</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4437</v>
+        <v>-1.2473</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1044</v>
+        <v>-0.5714</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.5225</v>
+        <v>-2.6101</v>
       </c>
       <c r="R14" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1851</v>
+        <v>0.0342</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0036</v>
+        <v>-0.0769</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1887</v>
+        <v>0.1111</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GRANGER</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8585</v>
+        <v>-0.297</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1929</v>
+        <v>-1.7425</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6656</v>
+        <v>1.4455</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6984</v>
+        <v>0.5628</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1065</v>
+        <v>-0.0213</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.5841</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4015</v>
+        <v>0.2235</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1743</v>
+        <v>-0.465</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2272</v>
+        <v>0.6885</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7031</v>
+        <v>0.3393</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2808</v>
+        <v>0.4437</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4224</v>
+        <v>-0.1044</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.6101</v>
+        <v>-1.5225</v>
       </c>
       <c r="R15" t="n">
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6216</v>
+        <v>-0.6423</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0156</v>
+        <v>-0.4434</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6373</v>
+        <v>-0.1989</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VAULET</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.908</v>
+        <v>-0.3076</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0254</v>
+        <v>0.154</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8827</v>
+        <v>-0.4616</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3425</v>
+        <v>0.2341</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8453000000000001</v>
+        <v>-0.1341</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5028</v>
+        <v>0.3682</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5437</v>
+        <v>1.5228</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3907</v>
+        <v>0.2007</v>
       </c>
       <c r="L16" t="n">
-        <v>0.153</v>
+        <v>1.322</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2012</v>
+        <v>-1.2887</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5453</v>
+        <v>-0.3348</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6558</v>
+        <v>-0.9539</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.6101</v>
+        <v>-1.305</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.293</v>
+        <v>-0.5417</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5239</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.231</v>
+        <v>-0.478</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>J. GRANGER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9819</v>
+        <v>-0.4565</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1812</v>
+        <v>-0.3047</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8007</v>
+        <v>-0.1518</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2341</v>
+        <v>0.6984</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1341</v>
+        <v>-0.1065</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3682</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5228</v>
+        <v>2.4015</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2007</v>
+        <v>1.1743</v>
       </c>
       <c r="L17" t="n">
-        <v>1.322</v>
+        <v>1.2272</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2887</v>
+        <v>-1.7031</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3348</v>
+        <v>-1.2808</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9539</v>
+        <v>-0.4224</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.305</v>
+        <v>-2.6101</v>
       </c>
       <c r="R17" t="n">
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.216</v>
+        <v>-0.2196</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.399</v>
+        <v>-0.0961</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.1235</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>J. VAULET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0876</v>
+        <v>-0.5213</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.543</v>
+        <v>0.3099</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5446</v>
+        <v>-0.8312</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9226</v>
+        <v>0.3425</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3473</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4247</v>
+        <v>-0.5028</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8961</v>
+        <v>2.5437</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1</v>
+        <v>2.3907</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9961</v>
+        <v>0.153</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8187</v>
+        <v>-2.2012</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2473</v>
+        <v>-1.5453</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5714</v>
+        <v>-0.6558</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0875</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.6101</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7725</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5239</v>
+        <v>-0.1887</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2485</v>
+        <v>0.2824</v>
       </c>
       <c r="V18" t="n">
-        <v>1.695</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>1.695</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1943</v>
+        <v>-0.9785</v>
       </c>
       <c r="E19" t="n">
         <v>-1.3308</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1365</v>
+        <v>0.3523</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1581</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0807</v>
+        <v>-0.8649</v>
       </c>
       <c r="T19" t="n">
         <v>-0.4795</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6012</v>
+        <v>-0.3854</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3904</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.727</v>
+        <v>-2.0962</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0455</v>
+        <v>-1.8907</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6815</v>
+        <v>-0.2055</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6021</v>
+        <v>0.0308</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0588</v>
+        <v>-1.6363</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4566</v>
+        <v>1.667</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6963</v>
+        <v>0.4006</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5816</v>
+        <v>-1.4354</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1147</v>
+        <v>1.836</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.3698</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4772</v>
+        <v>-0.2009</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5714</v>
+        <v>-0.1689</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.8276</v>
+        <v>-0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9151</v>
+        <v>-1.305</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4778</v>
+        <v>-0.8872</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0227</v>
+        <v>-0.6165</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.2707</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0207</v>
+        <v>-0.3698</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1507</v>
+        <v>-0.3698</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2503</v>
+        <v>-2.5953</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8907</v>
+        <v>-1.9396</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3596</v>
+        <v>-0.6558</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0308</v>
+        <v>0.6021</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6363</v>
+        <v>1.0588</v>
       </c>
       <c r="I22" t="n">
-        <v>1.667</v>
+        <v>-0.4566</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4006</v>
+        <v>0.6963</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4354</v>
+        <v>0.5816</v>
       </c>
       <c r="L22" t="n">
-        <v>1.836</v>
+        <v>0.1147</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3698</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2009</v>
+        <v>0.4772</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1689</v>
+        <v>-0.5714</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.87</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.305</v>
+        <v>-3.9151</v>
       </c>
       <c r="R22" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0413</v>
+        <v>-0.3906</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6165</v>
+        <v>0.1286</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4248</v>
+        <v>-0.5191</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3698</v>
+        <v>0.0207</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3698</v>
+        <v>1.1507</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0595</v>
+        <v>-3.026</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1614</v>
+        <v>-2.9379</v>
       </c>
       <c r="F23" t="n">
-        <v>0.102</v>
+        <v>-0.0881</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6721</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8017</v>
+        <v>-0.7682</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5179</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0602</v>
+        <v>-0.2503</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5857</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.7478</v>
+        <v>-11.2576</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.046</v>
+        <v>-10.0461</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7017</v>
+        <v>-1.2116</v>
       </c>
       <c r="G24" t="n">
         <v>-1.092</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6699000000000002</v>
+        <v>-0.6699000000000004</v>
       </c>
       <c r="I24" t="n">
         <v>-0.4222000000000006</v>
@@ -2305,7 +2305,7 @@
         <v>2.678499999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>3.701400000000001</v>
+        <v>3.7014</v>
       </c>
       <c r="M24" t="n">
         <v>-7.4723</v>
@@ -2317,7 +2317,7 @@
         <v>-4.1239</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.6126</v>
+        <v>-7.612599999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-18.4879</v>
@@ -2326,13 +2326,13 @@
         <v>10.875</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.3031</v>
+        <v>-4.813</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.064300000000001</v>
+        <v>-3.0643</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.2386</v>
+        <v>-1.7486</v>
       </c>
       <c r="V24" t="n">
         <v>2.26</v>
